--- a/workspace/Written Datasets/COR_MTX2.xlsx
+++ b/workspace/Written Datasets/COR_MTX2.xlsx
@@ -12,9 +12,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
   <si>
     <t xml:space="preserve">H2A Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2A_workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroughtNumberofEvents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroughtAnnualizedFrequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroughtExposureImpactedAreasqmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroughtExposureAgricultureValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DroughtExposureTotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveNumberofEvents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveAnnualizedFrequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveExposureImpactedAreasqmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveExposureBuildingValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveExposurePopulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveExposureAgricultureValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeatWaveExposureTotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireAnnualizedFrequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireExposureImpactedAreasqmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireExposureBuildingValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireExposurePopulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireExposureAgricultureValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WildfireExposureTotal</t>
   </si>
 </sst>
 </file>
@@ -347,120 +407,160 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
         <v>-0.28</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
         <v>-0.31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
         <v>0.07</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
         <v>0.53</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="n">
         <v>0.53</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
         <v>0.07</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
         <v>0.36</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="n">
         <v>0.37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
         <v>-0.15</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n">
         <v>0.42</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n">
         <v>0.33</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n">
         <v>0.09</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>-0.07</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.01</v>
       </c>
     </row>
   </sheetData>
